--- a/data/trans_orig/P16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82440</t>
+          <t>81952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116786</t>
+          <t>117598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>157248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198862</t>
+          <t>198328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249886</t>
+          <t>248718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303706</t>
+          <t>301250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377278</t>
+          <t>376466</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411624</t>
+          <t>412112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268627</t>
+          <t>269161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308475</t>
+          <t>310241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>657847</t>
+          <t>660303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711667</t>
+          <t>712835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125592</t>
+          <t>125890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172912</t>
+          <t>169890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247414</t>
+          <t>244260</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>298383</t>
+          <t>295660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386950</t>
+          <t>387101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453246</t>
+          <t>454910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562577</t>
+          <t>565599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>609897</t>
+          <t>609599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327111</t>
+          <t>329834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378080</t>
+          <t>381234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907736</t>
+          <t>906072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974032</t>
+          <t>973881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153341</t>
+          <t>151285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197625</t>
+          <t>196821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283816</t>
+          <t>288395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>337086</t>
+          <t>341060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>454199</t>
+          <t>451994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>522514</t>
+          <t>524054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440024</t>
+          <t>440828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>484308</t>
+          <t>486364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>352658</t>
+          <t>348684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>405928</t>
+          <t>401349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804880</t>
+          <t>803340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>875400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182875</t>
+          <t>184061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231637</t>
+          <t>228949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>270910</t>
+          <t>270304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>315584</t>
+          <t>312237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>465431</t>
+          <t>463043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>531258</t>
+          <t>533198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287510</t>
+          <t>290198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336272</t>
+          <t>335086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200058</t>
+          <t>203405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>244732</t>
+          <t>245338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503531</t>
+          <t>501591</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569358</t>
+          <t>571746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>263469</t>
+          <t>264866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297333</t>
+          <t>297362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285280</t>
+          <t>285917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319556</t>
+          <t>319593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>560703</t>
+          <t>561867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>609266</t>
+          <t>609684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89377</t>
+          <t>89348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123241</t>
+          <t>121844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84430</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118706</t>
+          <t>118069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181430</t>
+          <t>181012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229993</t>
+          <t>228829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216902</t>
+          <t>218554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244414</t>
+          <t>244351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>297082</t>
+          <t>297109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318725</t>
+          <t>318872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>522983</t>
+          <t>523316</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>557613</t>
+          <t>557781</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>74029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77904</t>
+          <t>77736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112534</t>
+          <t>112201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178048</t>
+          <t>177413</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194876</t>
+          <t>195150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>300238</t>
+          <t>300033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320849</t>
+          <t>319997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>484994</t>
+          <t>485364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>511159</t>
+          <t>511344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32632</t>
+          <t>32447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1273254</t>
+          <t>1278406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1384974</t>
+          <t>1386547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1917351</t>
+          <t>1921725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2039467</t>
+          <t>2034112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3224177</t>
+          <t>3225281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3385897</t>
+          <t>3389671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1890551</t>
+          <t>1888978</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2002271</t>
+          <t>1997119</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1339730</t>
+          <t>1345085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1461846</t>
+          <t>1457472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3268825</t>
+          <t>3265051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3430545</t>
+          <t>3429441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2012 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105522</t>
+          <t>107012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142989</t>
+          <t>146037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186433</t>
+          <t>187939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230124</t>
+          <t>229218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304844</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366091</t>
+          <t>363565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310116</t>
+          <t>307068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347583</t>
+          <t>346093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199215</t>
+          <t>200121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242906</t>
+          <t>241400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516354</t>
+          <t>518880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577601</t>
+          <t>578723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200624</t>
+          <t>200519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249465</t>
+          <t>253427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330673</t>
+          <t>331783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>379770</t>
+          <t>381640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544212</t>
+          <t>547929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>619054</t>
+          <t>616204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436773</t>
+          <t>432811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485614</t>
+          <t>485719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230485</t>
+          <t>228615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279582</t>
+          <t>278472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677439</t>
+          <t>680289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752281</t>
+          <t>748564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225563</t>
+          <t>228638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>277670</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>402717</t>
+          <t>403490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>459043</t>
+          <t>458874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>647462</t>
+          <t>645963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>723221</t>
+          <t>722578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402384</t>
+          <t>399963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454491</t>
+          <t>451416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250772</t>
+          <t>250941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307098</t>
+          <t>306325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666648</t>
+          <t>667291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>742407</t>
+          <t>743906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267068</t>
+          <t>262114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>318449</t>
+          <t>317482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>404009</t>
+          <t>401164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>451846</t>
+          <t>450962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>679320</t>
+          <t>684538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>755503</t>
+          <t>756149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296168</t>
+          <t>297135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347549</t>
+          <t>352503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163376</t>
+          <t>164260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211213</t>
+          <t>214058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474336</t>
+          <t>473690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550519</t>
+          <t>545301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304471</t>
+          <t>302758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340702</t>
+          <t>340360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>352105</t>
+          <t>351533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385961</t>
+          <t>387406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>667501</t>
+          <t>667860</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>718639</t>
+          <t>719421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87642</t>
+          <t>87984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123873</t>
+          <t>125586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61839</t>
+          <t>60394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95695</t>
+          <t>96267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>157505</t>
+          <t>156723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208643</t>
+          <t>208284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>262175</t>
+          <t>261592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>284976</t>
+          <t>284306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312896</t>
+          <t>311942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335248</t>
+          <t>334730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>581827</t>
+          <t>582903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>613596</t>
+          <t>614951</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81955</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>223757</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>240225</t>
+          <t>240338</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367271</t>
+          <t>367176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>382892</t>
+          <t>383489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>597392</t>
+          <t>597070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>619835</t>
+          <t>619491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41438</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1667748</t>
+          <t>1659947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1784240</t>
+          <t>1782840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2440594</t>
+          <t>2442542</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2553846</t>
+          <t>2556228</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4130658</t>
+          <t>4142304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4301986</t>
+          <t>4302665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1637754</t>
+          <t>1639154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1754246</t>
+          <t>1762047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001561</t>
+          <t>999179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1114813</t>
+          <t>1112865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2675415</t>
+          <t>2674736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2846743</t>
+          <t>2835097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77658</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111882</t>
+          <t>111236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152107</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189830</t>
+          <t>188818</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236052</t>
+          <t>239272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291543</t>
+          <t>291924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307581</t>
+          <t>308227</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341805</t>
+          <t>343445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205925</t>
+          <t>206937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243648</t>
+          <t>245065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523675</t>
+          <t>523294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579166</t>
+          <t>575946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170093</t>
+          <t>170300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214607</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>246501</t>
+          <t>242982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290495</t>
+          <t>290265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>427364</t>
+          <t>427961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>496397</t>
+          <t>493859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375889</t>
+          <t>374108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420403</t>
+          <t>420196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>273049</t>
+          <t>273279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317043</t>
+          <t>320562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>657643</t>
+          <t>660181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>726676</t>
+          <t>726079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220568</t>
+          <t>219262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270608</t>
+          <t>271446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>315814</t>
+          <t>314422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>367079</t>
+          <t>365169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550677</t>
+          <t>550972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>624464</t>
+          <t>626012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>398489</t>
+          <t>397651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448529</t>
+          <t>449835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294307</t>
+          <t>296217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345572</t>
+          <t>346964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>706019</t>
+          <t>704471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>779806</t>
+          <t>779511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>306326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360553</t>
+          <t>361943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>370782</t>
+          <t>370205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425074</t>
+          <t>421583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>692619</t>
+          <t>693641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>767774</t>
+          <t>769296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285495</t>
+          <t>284105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341950</t>
+          <t>339722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224003</t>
+          <t>227494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278295</t>
+          <t>278872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>527351</t>
+          <t>525829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602506</t>
+          <t>601484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>288474</t>
+          <t>289597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>333658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>374992</t>
+          <t>373372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413822</t>
+          <t>413441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676666</t>
+          <t>677593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>736798</t>
+          <t>738738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146153</t>
+          <t>144260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>188321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83027</t>
+          <t>83408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121857</t>
+          <t>123477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237969</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298101</t>
+          <t>297174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>265961</t>
+          <t>263278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>293380</t>
+          <t>292499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>335926</t>
+          <t>334022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>356602</t>
+          <t>356630</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>608386</t>
+          <t>608106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>643980</t>
+          <t>642258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>41831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68369</t>
+          <t>71052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68112</t>
+          <t>69834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103706</t>
+          <t>103986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>224817</t>
+          <t>224201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241723</t>
+          <t>241180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369552</t>
+          <t>368957</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>388842</t>
+          <t>388723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>600959</t>
+          <t>600675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>626427</t>
+          <t>625974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>56492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1633568</t>
+          <t>1631591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1750301</t>
+          <t>1748531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2232652</t>
+          <t>2246478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2355591</t>
+          <t>2364311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3910385</t>
+          <t>3906636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4079246</t>
+          <t>4069645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1644049</t>
+          <t>1645819</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1760782</t>
+          <t>1762759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1188951</t>
+          <t>1180231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1311890</t>
+          <t>1298064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2859646</t>
+          <t>2869247</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3028507</t>
+          <t>3032256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023</t>
+          <t>Población que ha utilizado algún tipo de medicamento en las últimas dos semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69441</t>
+          <t>72002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132162</t>
+          <t>133986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96405</t>
+          <t>97650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141283</t>
+          <t>141944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178955</t>
+          <t>180543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253131</t>
+          <t>258723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267825</t>
+          <t>266001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330546</t>
+          <t>327985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171917</t>
+          <t>171256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216795</t>
+          <t>215550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460056</t>
+          <t>454464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>534232</t>
+          <t>532644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117485</t>
+          <t>118989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169031</t>
+          <t>170236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226389</t>
+          <t>226998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357137</t>
+          <t>369320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361595</t>
+          <t>360376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>530964</t>
+          <t>548565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254516</t>
+          <t>253311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306062</t>
+          <t>304558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154367</t>
+          <t>142184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>285115</t>
+          <t>284506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404087</t>
+          <t>386486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>573456</t>
+          <t>574675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188670</t>
+          <t>187455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235371</t>
+          <t>235041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253628</t>
+          <t>254736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293017</t>
+          <t>292812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452915</t>
+          <t>453616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>515530</t>
+          <t>518093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300967</t>
+          <t>301297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347668</t>
+          <t>348883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249451</t>
+          <t>249656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288840</t>
+          <t>287732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563276</t>
+          <t>560713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625891</t>
+          <t>625190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146578</t>
+          <t>143183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>465039</t>
+          <t>463355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>347869</t>
+          <t>344491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449165</t>
+          <t>448413</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>428954</t>
+          <t>470664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>900858</t>
+          <t>901229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422747</t>
+          <t>424431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>741208</t>
+          <t>744603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>263716</t>
+          <t>264468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365012</t>
+          <t>368390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699809</t>
+          <t>699438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1171713</t>
+          <t>1130003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>375472</t>
+          <t>378275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>418200</t>
+          <t>416846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396292</t>
+          <t>394139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>426279</t>
+          <t>423231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>782513</t>
+          <t>782471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>832487</t>
+          <t>830667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143034</t>
+          <t>144388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185762</t>
+          <t>182959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118608</t>
+          <t>121656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148595</t>
+          <t>150748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273634</t>
+          <t>275454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323608</t>
+          <t>323650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>268876</t>
+          <t>268013</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>295438</t>
+          <t>294607</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>500822</t>
+          <t>500725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580657</t>
+          <t>577322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>775348</t>
+          <t>775969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>889242</t>
+          <t>895782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99289</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>107643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87291</t>
+          <t>80751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201185</t>
+          <t>200564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>233495</t>
+          <t>234327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>252449</t>
+          <t>252603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>381711</t>
+          <t>380618</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>398928</t>
+          <t>397712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>619708</t>
+          <t>622010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>645418</t>
+          <t>647174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>30156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62631</t>
+          <t>60875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88341</t>
+          <t>86039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1310152</t>
+          <t>1322592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1859567</t>
+          <t>1860030</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2317771</t>
+          <t>2308673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2679727</t>
+          <t>2627814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3634249</t>
+          <t>3690438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4375000</t>
+          <t>4383430</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1600250</t>
+          <t>1599787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2149665</t>
+          <t>2137225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>978871</t>
+          <t>1030784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1340827</t>
+          <t>1349925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2743415</t>
+          <t>2734985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3484166</t>
+          <t>3427977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81952</t>
+          <t>81754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117598</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157248</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198328</t>
+          <t>196284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248718</t>
+          <t>249695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301250</t>
+          <t>305240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>376561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412112</t>
+          <t>412310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269161</t>
+          <t>271205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310241</t>
+          <t>310109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>656313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712835</t>
+          <t>711858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125890</t>
+          <t>127337</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169890</t>
+          <t>168596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244260</t>
+          <t>246846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>295660</t>
+          <t>296676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387101</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>454910</t>
+          <t>456181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565599</t>
+          <t>566893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>609599</t>
+          <t>608152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329834</t>
+          <t>328818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>381234</t>
+          <t>378648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906072</t>
+          <t>904801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973881</t>
+          <t>975972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>152262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196821</t>
+          <t>196534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>288395</t>
+          <t>284475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341060</t>
+          <t>337330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>451994</t>
+          <t>451499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524054</t>
+          <t>521962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440828</t>
+          <t>441115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>486364</t>
+          <t>485387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>348684</t>
+          <t>352414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>401349</t>
+          <t>405269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>803340</t>
+          <t>805432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875400</t>
+          <t>875895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184061</t>
+          <t>183103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228949</t>
+          <t>229626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>270304</t>
+          <t>267403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312237</t>
+          <t>314430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463043</t>
+          <t>467703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533198</t>
+          <t>531050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290198</t>
+          <t>289521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335086</t>
+          <t>336044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203405</t>
+          <t>201212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245338</t>
+          <t>248239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>501591</t>
+          <t>503739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>571746</t>
+          <t>567086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264866</t>
+          <t>263545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297362</t>
+          <t>298679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285917</t>
+          <t>285458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319593</t>
+          <t>320209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>561867</t>
+          <t>559780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>609684</t>
+          <t>610686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89348</t>
+          <t>88031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121844</t>
+          <t>123165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84393</t>
+          <t>83777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118069</t>
+          <t>118528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181012</t>
+          <t>180010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228829</t>
+          <t>230916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>218554</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244351</t>
+          <t>244509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>297109</t>
+          <t>296006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318872</t>
+          <t>317936</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>523316</t>
+          <t>523244</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>557781</t>
+          <t>558332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74029</t>
+          <t>75616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>46928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77736</t>
+          <t>77185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112201</t>
+          <t>112273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177413</t>
+          <t>178170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195150</t>
+          <t>194859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>300033</t>
+          <t>300781</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>319997</t>
+          <t>320149</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>485364</t>
+          <t>484675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>511344</t>
+          <t>510687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>59116</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1278406</t>
+          <t>1269227</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1386547</t>
+          <t>1384329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1921725</t>
+          <t>1919943</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2034112</t>
+          <t>2033055</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3225281</t>
+          <t>3227741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3389671</t>
+          <t>3384674</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1888978</t>
+          <t>1891196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1997119</t>
+          <t>2006298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1345085</t>
+          <t>1346142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1457472</t>
+          <t>1459254</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3265051</t>
+          <t>3270048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3429441</t>
+          <t>3426981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>105475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146037</t>
+          <t>145347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187939</t>
+          <t>187747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229218</t>
+          <t>230133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303722</t>
+          <t>305835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>363565</t>
+          <t>363614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307068</t>
+          <t>307758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346093</t>
+          <t>347630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200121</t>
+          <t>199206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241400</t>
+          <t>241592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518880</t>
+          <t>518831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578723</t>
+          <t>576610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200519</t>
+          <t>199963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253427</t>
+          <t>248828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331783</t>
+          <t>330299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>381640</t>
+          <t>380612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547929</t>
+          <t>546873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>616204</t>
+          <t>620091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432811</t>
+          <t>437410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485719</t>
+          <t>486275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228615</t>
+          <t>229643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278472</t>
+          <t>279956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680289</t>
+          <t>676402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748564</t>
+          <t>749620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>228638</t>
+          <t>227341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280091</t>
+          <t>279857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>403490</t>
+          <t>403975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>458874</t>
+          <t>458139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645963</t>
+          <t>646850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722578</t>
+          <t>723831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>399963</t>
+          <t>400197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451416</t>
+          <t>452713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250941</t>
+          <t>251676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306325</t>
+          <t>305840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667291</t>
+          <t>666038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>743906</t>
+          <t>743019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>262114</t>
+          <t>265255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317482</t>
+          <t>315573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>401164</t>
+          <t>401771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>450962</t>
+          <t>449963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684538</t>
+          <t>679803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>756149</t>
+          <t>755341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297135</t>
+          <t>299044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352503</t>
+          <t>349362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164260</t>
+          <t>165259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214058</t>
+          <t>213451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>473690</t>
+          <t>474498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>545301</t>
+          <t>550036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302758</t>
+          <t>302849</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340360</t>
+          <t>342133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351533</t>
+          <t>353836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>387406</t>
+          <t>387553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>667860</t>
+          <t>667153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>719421</t>
+          <t>718268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87984</t>
+          <t>86211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125586</t>
+          <t>125495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>60247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96267</t>
+          <t>93964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156723</t>
+          <t>157876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208284</t>
+          <t>208991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>261592</t>
+          <t>261593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>284306</t>
+          <t>283632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>311942</t>
+          <t>313479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>334730</t>
+          <t>334540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>582903</t>
+          <t>582886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>614951</t>
+          <t>614871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48194</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80879</t>
+          <t>80896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>223864</t>
+          <t>224604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>240338</t>
+          <t>240333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367176</t>
+          <t>366890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383489</t>
+          <t>382498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>597070</t>
+          <t>597546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>619491</t>
+          <t>620127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>22089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>41284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1659947</t>
+          <t>1663558</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1782840</t>
+          <t>1785559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2442542</t>
+          <t>2442617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2556228</t>
+          <t>2556595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4142304</t>
+          <t>4138554</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4302665</t>
+          <t>4304306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1639154</t>
+          <t>1636435</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1762047</t>
+          <t>1758436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>999179</t>
+          <t>998812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1112865</t>
+          <t>1112790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2674736</t>
+          <t>2673095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2835097</t>
+          <t>2838847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>76746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111236</t>
+          <t>111768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>152053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188818</t>
+          <t>190737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239272</t>
+          <t>239613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291924</t>
+          <t>291791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308227</t>
+          <t>307695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>343445</t>
+          <t>342717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206937</t>
+          <t>205018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245065</t>
+          <t>243702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523294</t>
+          <t>523427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575946</t>
+          <t>575605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170300</t>
+          <t>170263</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216388</t>
+          <t>214315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,82 +7049,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>267386</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>243790</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>291816</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>43,26%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>51,78%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>459489</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>422928</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>492530</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>39,82%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>36,65%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>267386</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>242982</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>290265</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>459489</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>427961</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>493859</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>37,08%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374108</t>
+          <t>376181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420196</t>
+          <t>420233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,82 +7162,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>63,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>296158</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>271728</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>319754</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>48,22%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>56,74%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>694551</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>661510</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>731112</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>60,18%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>57,32%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>63,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>296158</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>273279</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>320562</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>52,55%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>48,49%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>56,88%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>694551</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>660181</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>726079</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>60,18%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>57,21%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219262</t>
+          <t>219572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271446</t>
+          <t>270494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>314422</t>
+          <t>316561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365169</t>
+          <t>364692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550972</t>
+          <t>553236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626012</t>
+          <t>621036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397651</t>
+          <t>398603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449835</t>
+          <t>449525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296217</t>
+          <t>296694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346964</t>
+          <t>344825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>704471</t>
+          <t>709447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>779511</t>
+          <t>777247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>306326</t>
+          <t>307849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>361943</t>
+          <t>362631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>370205</t>
+          <t>370465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>421583</t>
+          <t>421216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>693641</t>
+          <t>698096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>769296</t>
+          <t>768558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284105</t>
+          <t>283417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339722</t>
+          <t>338199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227494</t>
+          <t>227861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278872</t>
+          <t>278612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525829</t>
+          <t>526567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601484</t>
+          <t>597029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289597</t>
+          <t>289603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>333658</t>
+          <t>332149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>373372</t>
+          <t>373515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413441</t>
+          <t>414191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677593</t>
+          <t>673243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738738</t>
+          <t>731716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144260</t>
+          <t>145769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188321</t>
+          <t>188315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83408</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123477</t>
+          <t>123334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236029</t>
+          <t>243051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297174</t>
+          <t>301524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>263278</t>
+          <t>266400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>292499</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>334022</t>
+          <t>333080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>356159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>608106</t>
+          <t>608724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>642258</t>
+          <t>642840</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>41097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71052</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>44682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69834</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103986</t>
+          <t>103368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>224201</t>
+          <t>224670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241180</t>
+          <t>241795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368957</t>
+          <t>369808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>388723</t>
+          <t>389101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>600675</t>
+          <t>602462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>625974</t>
+          <t>626335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31193</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56492</t>
+          <t>54705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1631591</t>
+          <t>1631125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1748531</t>
+          <t>1744987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2246478</t>
+          <t>2242521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2364311</t>
+          <t>2360411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3906636</t>
+          <t>3904331</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4069645</t>
+          <t>4081280</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1645819</t>
+          <t>1649363</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1762759</t>
+          <t>1763225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1180231</t>
+          <t>1184131</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1298064</t>
+          <t>1302021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2869247</t>
+          <t>2857612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3032256</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99913</t>
+          <t>102521</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>74457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133986</t>
+          <t>130656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>117456</t>
+          <t>139883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>115280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141944</t>
+          <t>166009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>217369</t>
+          <t>242405</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180543</t>
+          <t>206515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258723</t>
+          <t>283246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>300074</t>
+          <t>305272</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266001</t>
+          <t>277137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327985</t>
+          <t>333336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195744</t>
+          <t>222629</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171256</t>
+          <t>196503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215550</t>
+          <t>247232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>495818</t>
+          <t>527900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454464</t>
+          <t>487059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532644</t>
+          <t>563790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>143654</t>
+          <t>156498</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118989</t>
+          <t>128859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170236</t>
+          <t>182371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>271992</t>
+          <t>219305</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226998</t>
+          <t>195602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>369320</t>
+          <t>242548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>415646</t>
+          <t>375802</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>360376</t>
+          <t>337353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>548565</t>
+          <t>411233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>279893</t>
+          <t>320392</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253311</t>
+          <t>294519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304558</t>
+          <t>348031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>239512</t>
+          <t>281778</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142184</t>
+          <t>258535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>284506</t>
+          <t>305481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>519405</t>
+          <t>602171</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386486</t>
+          <t>566740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>574675</t>
+          <t>640620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>210309</t>
+          <t>232898</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187455</t>
+          <t>207167</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235041</t>
+          <t>259290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>272869</t>
+          <t>310083</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>254736</t>
+          <t>289206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292812</t>
+          <t>332880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>483178</t>
+          <t>542981</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453616</t>
+          <t>511942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>518093</t>
+          <t>576875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>326029</t>
+          <t>387939</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301297</t>
+          <t>361547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>348883</t>
+          <t>413670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>269599</t>
+          <t>312056</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249656</t>
+          <t>289259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287732</t>
+          <t>332933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>595628</t>
+          <t>699995</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560713</t>
+          <t>666101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625190</t>
+          <t>731034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>327224</t>
+          <t>352583</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143183</t>
+          <t>323133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>463355</t>
+          <t>379703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>420183</t>
+          <t>449254</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>344491</t>
+          <t>428978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>448413</t>
+          <t>471856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>747408</t>
+          <t>801837</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470664</t>
+          <t>768409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>901229</t>
+          <t>835750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>560562</t>
+          <t>348034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>424431</t>
+          <t>320914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>744603</t>
+          <t>377484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>292698</t>
+          <t>287632</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264468</t>
+          <t>265030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368390</t>
+          <t>307908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>853259</t>
+          <t>635667</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699438</t>
+          <t>601754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1130003</t>
+          <t>669095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>397403</t>
+          <t>422419</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>378275</t>
+          <t>400749</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>416846</t>
+          <t>445440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>409839</t>
+          <t>455890</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>394139</t>
+          <t>439402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>423231</t>
+          <t>472009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>807242</t>
+          <t>878309</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>782471</t>
+          <t>849643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>830667</t>
+          <t>905393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>163831</t>
+          <t>186927</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144388</t>
+          <t>163906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182959</t>
+          <t>208597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135048</t>
+          <t>151558</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121656</t>
+          <t>135439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150748</t>
+          <t>168046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>298879</t>
+          <t>338485</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275454</t>
+          <t>311401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323650</t>
+          <t>367151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106121</t>
+          <t>1216794</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>282870</t>
+          <t>311188</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>268013</t>
+          <t>297080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>294607</t>
+          <t>326051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>540461</t>
+          <t>365907</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>500725</t>
+          <t>353072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>577322</t>
+          <t>376414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>823331</t>
+          <t>677095</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>775969</t>
+          <t>656615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>895782</t>
+          <t>695398</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>95892</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>81029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100152</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>73259</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107643</t>
+          <t>86094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>153202</t>
+          <t>169151</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80751</t>
+          <t>150848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200564</t>
+          <t>189631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>244253</t>
+          <t>267190</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234327</t>
+          <t>254080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>252603</t>
+          <t>277204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>390151</t>
+          <t>424254</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>380618</t>
+          <t>413321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>397712</t>
+          <t>432740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>634403</t>
+          <t>691444</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>622010</t>
+          <t>676789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>647174</t>
+          <t>706077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>43008</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48432</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>31266</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>73646</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60875</t>
+          <t>68127</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86039</t>
+          <t>97415</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1705627</t>
+          <t>1845298</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1322592</t>
+          <t>1778416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1860030</t>
+          <t>1909063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2422952</t>
+          <t>2364576</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2308673</t>
+          <t>2312258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2627814</t>
+          <t>2418038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4128578</t>
+          <t>4209874</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3690438</t>
+          <t>4126631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4383430</t>
+          <t>4298084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1754190</t>
+          <t>1687464</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1599787</t>
+          <t>1623699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2137225</t>
+          <t>1754346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1235646</t>
+          <t>1368665</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1030784</t>
+          <t>1315203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1349925</t>
+          <t>1420983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2989837</t>
+          <t>3056129</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2734985</t>
+          <t>2967919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3427977</t>
+          <t>3139372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
